--- a/feedback_forms/047_harp_performance_feedback_survey--feedback_forms.xlsx
+++ b/feedback_forms/047_harp_performance_feedback_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'text':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'text': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'text':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'text': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'text':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'text': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'text':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'text': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'text':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'text': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'text':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'text': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'text':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'text': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'text':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'text': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'text':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'text': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1500,12 +1500,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'text':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'text': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1534,12 +1534,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1568,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'text':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'text': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'text':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'text': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'text':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'text': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1619,12 +1619,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'text':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'text': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'text':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'text': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1653,12 +1653,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'text':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'text': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'text':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'text': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'text':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'text': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'text':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'text': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'text':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'text': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'text':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'text': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
